--- a/input/Tăng ca_20220118002655.xlsx
+++ b/input/Tăng ca_20220118002655.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24729"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SkyTam\Desktop\cham-cong\input\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC061C3D-0065-4943-9CF8-20DD22E85A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20220118" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>Tăng ca</t>
   </si>
@@ -46,25 +52,10 @@
     <t>Trạng thái phê duyệt</t>
   </si>
   <si>
-    <t>A055</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Dung Em</t>
-  </si>
-  <si>
     <t>X1 Xi Line 1-1</t>
   </si>
   <si>
     <t>Xin làm thêm</t>
-  </si>
-  <si>
-    <t>2021-01-16 06:00:00</t>
-  </si>
-  <si>
-    <t>2022-01-16 12:00:00</t>
-  </si>
-  <si>
-    <t>2022-01-18 00:12:19</t>
   </si>
   <si>
     <t>Phê duyệt</t>
@@ -100,8 +91,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,26 +162,34 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Chủ đề Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -232,7 +231,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -264,9 +263,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -298,6 +315,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -473,9 +508,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
@@ -488,20 +523,20 @@
     <col min="9" max="9" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+    <row r="1" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -514,114 +549,87 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="E4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -630,5 +638,6 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>